--- a/docs/Kエナジー_DD/チェックシート/PX案件チェックシート_1747_伊豆の国.xlsx
+++ b/docs/Kエナジー_DD/チェックシート/PX案件チェックシート_1747_伊豆の国.xlsx
@@ -2973,7 +2973,7 @@
       <c r="E17" s="9" t="inlineStr"/>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>輸送可否（可／要対策／不可）と必要対策。 / ①伊豆の国市へ開発許可の事前相談（市街化調整区域） ②丘の上の造成計画（切土・盛土量）を概算 ③田方変電所への接続可否を確認</t>
+          <t>輸送可否（可／要対策／不可）と必要対策。 / ①伊豆の国市へ開発許可の事前相談（市街化調整区域） ②田方154kVに余裕がないため接続可否を電力会社へ事前相談 ③丘の上の造成計画（切土・盛土量）を概算</t>
         </is>
       </c>
     </row>
